--- a/game-stats/Week7_Warriors_vs_K2.xlsx
+++ b/game-stats/Week7_Warriors_vs_K2.xlsx
@@ -4174,7 +4174,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
@@ -4186,7 +4186,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>0</v>

--- a/game-stats/Week7_Warriors_vs_K2.xlsx
+++ b/game-stats/Week7_Warriors_vs_K2.xlsx
@@ -5083,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="7" t="n">
         <v>0</v>
